--- a/data/Fragebogen_ Sense of Belonging im Studium (Responses).xlsx
+++ b/data/Fragebogen_ Sense of Belonging im Studium (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="202">
   <si>
     <t>Timestamp</t>
   </si>
@@ -435,6 +435,192 @@
   </si>
   <si>
     <t>Die Hochschule kann da recht wenig dran ändern. Das sind tiefst soziologische und generationelle Entwicklungen die nur eine nachfolgende Generation hoffentlich bessern kann.</t>
+  </si>
+  <si>
+    <t>Ich habe mich durch meine Familie unter Druck gesetzt gefühlt.</t>
+  </si>
+  <si>
+    <t>Studienstart, Mitte des Studiums</t>
+  </si>
+  <si>
+    <t>Studienberatung, Psychologische Beratung, Finanzielle Unterstützung</t>
+  </si>
+  <si>
+    <t>Austausch mit anderen Studierenden, Gute Organisation des Studiums, Unterstützung durch Dozierende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenn keine Transparenz durch Dozierende betreffend Modulaufbau und -ablauf gemacht werden, da ich als Teilzeitstudent nicht jede Vorlesung immer besuchen kann. </t>
+  </si>
+  <si>
+    <t>Transparenz betreffend Modulen, also Ablauf des Semester, behandelte Themen</t>
+  </si>
+  <si>
+    <t>Stair Events</t>
+  </si>
+  <si>
+    <t>Mehr Events. Auch mal nur Klassenweise</t>
+  </si>
+  <si>
+    <t>Bessere Karrierechancen, Gesellschaftlicher Aufstieg</t>
+  </si>
+  <si>
+    <t>Mitte des Studiums, Abschlussphase</t>
+  </si>
+  <si>
+    <t>Bessere unterstützung für teilzeit studenten, wir studieren Trilzeit weil wir kein geld haben und jetzt ist der wipro infotag am montag und dienstag, an unseren arbeitstagen</t>
+  </si>
+  <si>
+    <t>Möchte ich nicht angeben</t>
+  </si>
+  <si>
+    <t>Wenn wir teilzeitstundenten systematisch von infoanlässen ausgeschlossen werden</t>
+  </si>
+  <si>
+    <t>Am besten, in dem mann rücksicht auf teilzeit studenten nimmt</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Keine</t>
+  </si>
+  <si>
+    <t>Nichts</t>
+  </si>
+  <si>
+    <t>Persönliche Entwicklung</t>
+  </si>
+  <si>
+    <t>Mehr Mentoring</t>
+  </si>
+  <si>
+    <t>Unterstützung durch Dozierende, Mentoringprogramme</t>
+  </si>
+  <si>
+    <t>Ungezwungene Gruppenarbeiten</t>
+  </si>
+  <si>
+    <t>Spontane Gruppenübungen</t>
+  </si>
+  <si>
+    <t>Interesse am Fach, Bessere Karrierechancen, Empfehlung von Familie / Freunden, Persönliche Entwicklung</t>
+  </si>
+  <si>
+    <t>Mehr Mentoring, Bessere Informationen zum Studium</t>
+  </si>
+  <si>
+    <t>Zeit mit anderen Studenten verbringen</t>
+  </si>
+  <si>
+    <t>Studienberatung, Mentoringprogramme, Psychologische Beratung</t>
+  </si>
+  <si>
+    <t>Bessere Karrierechancen, Persönliche Entwicklung</t>
+  </si>
+  <si>
+    <t>Mehr Mentoring, Finanzielle Unterstützung</t>
+  </si>
+  <si>
+    <t>Die richtigen Freunde zu finden, die auf der gleichen "Wellenlänge" sind und unter gleichen Umständen studieren.</t>
+  </si>
+  <si>
+    <t>Wenn ich mich mit anderen Studierenden vergleiche</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Bessere Informationen zum Studium, Karriereberatung, Austausch mit anderen Studierenden</t>
+  </si>
+  <si>
+    <t>Business Administration: Banking &amp; Finance</t>
+  </si>
+  <si>
+    <t>Kaffee</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>gratis Kaffee</t>
+  </si>
+  <si>
+    <t>Studienberatung, Mentoringprogramme, Psychologische Beratung, Finanzielle Unterstützung</t>
+  </si>
+  <si>
+    <t>Unterstützung durch Freunde, Austausch mit anderen Studierenden, Unterstützung durch Dozierende</t>
+  </si>
+  <si>
+    <t>Die anderen Studenten</t>
+  </si>
+  <si>
+    <t>Nie</t>
+  </si>
+  <si>
+    <t>Passt so wie es ist</t>
+  </si>
+  <si>
+    <t>Freunde finden</t>
+  </si>
+  <si>
+    <t>de gäbu</t>
+  </si>
+  <si>
+    <t>wenn de gäbu mich mobbt</t>
+  </si>
+  <si>
+    <t>gäbu sött nüm mobbe</t>
+  </si>
+  <si>
+    <t>Ein Studium galt in meiner Familie als selbstverständlich.</t>
+  </si>
+  <si>
+    <t>Bessere Informationen zum Studium</t>
+  </si>
+  <si>
+    <t>Mehr Mentoring, Bessere Informationen zum Studium, Karriereberatung</t>
+  </si>
+  <si>
+    <t>freunde / mitstudierende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bessere Karrierechancen, Empfehlung von Familie / Freunden, </t>
+  </si>
+  <si>
+    <t>neue freunde</t>
+  </si>
+  <si>
+    <t>wenn ich nicht verstehe um was es geht, und die privaten Interessen oder der Humor der Mitstudierenden und mir sich grundlegend unterscheiden, was aber im Ordnung ist. Es stört mich nicht.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money </t>
+  </si>
+  <si>
+    <t>Studienstart, Erste Prüfungsphase, Mitte des Studiums, Abschlussphase</t>
+  </si>
+  <si>
+    <t>Mehr Mentoring, Bessere Informationen zum Studium, Finanzielle Unterstützung, Karriereberatung, Austausch mit anderen Studierenden</t>
+  </si>
+  <si>
+    <t>Harzhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei Informatik studis </t>
+  </si>
+  <si>
+    <t>Unterstützung durch Familie, Unterstützung durch Freunde, Austausch mit anderen Studierenden, Unterstützung durch Dozierende</t>
+  </si>
+  <si>
+    <t>Lehrperson</t>
+  </si>
+  <si>
+    <t>Studienstart</t>
+  </si>
+  <si>
+    <t>Austausch mit anderen Studierenden, Unterstützung durch Dozierende</t>
+  </si>
+  <si>
+    <t>Mehr Events</t>
   </si>
 </sst>
 </file>
@@ -572,7 +758,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AT31" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AT58" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="46">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Ich fühle mich an meiner Hochschule willkommen. " id="2"/>
@@ -4267,6 +4453,3105 @@
         <v>139</v>
       </c>
     </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="5">
+        <v>46132.90560373843</v>
+      </c>
+      <c r="B32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G32" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H32" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J32" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K32" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L32" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="M32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T32" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="W32" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="X32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE32" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF32" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH32" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI32" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ32" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AK32" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AL32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM32" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO32" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP32" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT32" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="5">
+        <v>46134.6009219213</v>
+      </c>
+      <c r="B33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E33" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H33" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I33" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="J33" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O33" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="P33" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R33" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S33" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T33" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>2029.0</v>
+      </c>
+      <c r="AP33" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AT33" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="5">
+        <v>46135.44701024306</v>
+      </c>
+      <c r="B34" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C34" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="D34" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E34" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F34" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G34" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I34" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J34" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="K34" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L34" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O34" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="P34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="R34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="S34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="T34" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM34" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP34" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ34" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="5">
+        <v>46135.44948782407</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="D35" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E35" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F35" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I35" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="K35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="M35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="N35" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="O35" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="P35" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="R35" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S35" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T35" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V35" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="W35" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD35" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE35" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG35" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH35" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AK35" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AL35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM35" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO35" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS35" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="AT35" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="5">
+        <v>46135.53455465278</v>
+      </c>
+      <c r="B36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F36" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H36" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="K36" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N36" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="P36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T36" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>2028.0</v>
+      </c>
+      <c r="AP36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AS36" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AT36" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="5">
+        <v>46135.562339861106</v>
+      </c>
+      <c r="B37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="J37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="M37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P37" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="R37" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="S37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V37" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="W37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y37" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z37" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD37" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE37" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG37" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH37" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI37" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ37" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AK37" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AL37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN37" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO37" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ37" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="5">
+        <v>46135.58104217592</v>
+      </c>
+      <c r="B38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F38" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="G38" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H38" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J38" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K38" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L38" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N38" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="O38" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P38" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R38" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S38" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="T38" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL38" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM38" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO38" s="6">
+        <v>2028.0</v>
+      </c>
+      <c r="AP38" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ38" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="5">
+        <v>46135.600114456014</v>
+      </c>
+      <c r="B39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D39" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F39" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I39" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="J39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K39" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L39" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="M39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N39" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="O39" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="P39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R39" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W39" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y39" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD39" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE39" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH39" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AL39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM39" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>2028.0</v>
+      </c>
+      <c r="AP39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR39" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AS39" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="5">
+        <v>46136.46255324074</v>
+      </c>
+      <c r="B40" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I40" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K40" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="L40" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N40" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="O40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P40" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R40" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S40" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="T40" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V40" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="W40" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD40" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG40" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="AH40" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI40" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ40" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AK40" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AL40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN40" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO40" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR40" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="5">
+        <v>46136.48020384259</v>
+      </c>
+      <c r="B41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G41" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H41" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J41" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K41" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="O41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="P41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R41" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S41" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T41" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W41" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X41" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z41" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD41" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE41" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH41" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI41" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AJ41" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AK41" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AL41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO41" s="6">
+        <v>2026.0</v>
+      </c>
+      <c r="AP41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="5">
+        <v>46136.509089942134</v>
+      </c>
+      <c r="B42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F42" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J42" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K42" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="L42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M42" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N42" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="O42" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="P42" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S42" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="T42" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM42" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP42" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ42" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="5">
+        <v>46139.52009706019</v>
+      </c>
+      <c r="B43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J43" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K43" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="L43" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="O43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R43" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T43" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U43" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL43" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP43" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ43" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="5">
+        <v>46139.628790462964</v>
+      </c>
+      <c r="B44" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C44" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D44" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="K44" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L44" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M44" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N44" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O44" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="P44" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="R44" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S44" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T44" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V44" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="W44" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X44" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y44" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA44" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC44" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD44" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG44" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI44" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AJ44" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AK44" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AL44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO44" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ44" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR44" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AS44" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="AT44" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="5">
+        <v>46141.34487449074</v>
+      </c>
+      <c r="B45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G45" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H45" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="K45" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="L45" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="M45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="P45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T45" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U45" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V45" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="W45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG45" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH45" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI45" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AJ45" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AK45" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AL45" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO45" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP45" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ45" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="5">
+        <v>46141.34731030093</v>
+      </c>
+      <c r="B46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T46" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U46" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL46" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP46" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ46" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AR46" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="AS46" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="AT46" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="5">
+        <v>46141.63472973379</v>
+      </c>
+      <c r="B47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="K47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="L47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N47" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="O47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T47" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U47" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="W47" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE47" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH47" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI47" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ47" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AK47" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AL47" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM47" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN47" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO47" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP47" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ47" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR47" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AS47" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AT47" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="5">
+        <v>46141.64021133102</v>
+      </c>
+      <c r="B48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="L48" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R48" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S48" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="T48" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U48" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL48" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM48" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN48" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO48" s="6">
+        <v>2026.0</v>
+      </c>
+      <c r="AP48" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ48" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR48" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="5">
+        <v>46141.64965520833</v>
+      </c>
+      <c r="B49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="C49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="J49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="L49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="N49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="O49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="P49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="R49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="S49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="T49" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL49" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM49" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN49" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO49" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP49" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ49" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR49" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="AS49" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT49" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="5">
+        <v>46141.90975869213</v>
+      </c>
+      <c r="B50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H50" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I50" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J50" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="K50" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O50" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="P50" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R50" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S50" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T50" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U50" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V50" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="W50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="X50" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y50" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z50" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA50" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB50" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC50" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD50" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE50" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF50" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG50" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="AH50" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AL50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN50" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP50" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ50" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="5">
+        <v>46146.6306312963</v>
+      </c>
+      <c r="B51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D51" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E51" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H51" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I51" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J51" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M51" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R51" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM51" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN51" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>2026.0</v>
+      </c>
+      <c r="AP51" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ51" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="5">
+        <v>46149.6245519213</v>
+      </c>
+      <c r="B52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="K52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="M52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T52" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U52" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="W52" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y52" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD52" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE52" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF52" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG52" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="AH52" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AK52" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AL52" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN52" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO52" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP52" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ52" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="5">
+        <v>46149.62503649306</v>
+      </c>
+      <c r="B53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="L53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="R53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S53" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T53" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U53" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V53" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="W53" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X53" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y53" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z53" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA53" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB53" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC53" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD53" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE53" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF53" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG53" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH53" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AL53" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM53" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN53" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>2026.0</v>
+      </c>
+      <c r="AP53" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR53" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="5">
+        <v>46149.63316978009</v>
+      </c>
+      <c r="B54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I54" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="J54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K54" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="L54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M54" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="N54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="R54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U54" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="W54" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X54" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z54" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA54" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB54" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD54" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE54" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF54" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG54" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH54" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI54" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ54" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AK54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AL54" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN54" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AO54" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP54" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR54" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AS54" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="5">
+        <v>46149.67497475694</v>
+      </c>
+      <c r="B55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E55" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="F55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I55" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J55" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K55" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="M55" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N55" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O55" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="P55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="R55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="U55" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V55" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="W55" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X55" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y55" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z55" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA55" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB55" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC55" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD55" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE55" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF55" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG55" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="AH55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AL55" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM55" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN55" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP55" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ55" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR55" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AS55" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="5">
+        <v>46149.69610267361</v>
+      </c>
+      <c r="B56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D56" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E56" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F56" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L56" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="M56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R56" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T56" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="U56" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V56" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="W56" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="X56" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y56" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z56" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA56" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB56" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC56" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD56" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE56" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF56" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH56" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI56" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AJ56" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AK56" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="AL56" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM56" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN56" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO56" s="6">
+        <v>2027.0</v>
+      </c>
+      <c r="AP56" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ56" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="5">
+        <v>46149.77328458334</v>
+      </c>
+      <c r="B57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D57" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="F57" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G57" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="K57" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="L57" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="M57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N57" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="O57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="P57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="R57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="T57" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U57" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V57" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="W57" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="X57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y57" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z57" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC57" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD57" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE57" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF57" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG57" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH57" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI57" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="AJ57" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="AK57" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="AL57" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM57" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN57" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO57" s="6">
+        <v>2026.0</v>
+      </c>
+      <c r="AP57" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ57" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT57" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="5">
+        <v>46151.4044180787</v>
+      </c>
+      <c r="B58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D58" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E58" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G58" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H58" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="I58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="J58" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="K58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="L58" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="M58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="N58" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="O58" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="P58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="R58" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S58" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="T58" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="U58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM58" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>2029.0</v>
+      </c>
+      <c r="AP58" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ58" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">
